--- a/MAJEntreesCDA/ig/StructureDefinition-fr-cda-acte-substitution.xlsx
+++ b/MAJEntreesCDA/ig/StructureDefinition-fr-cda-acte-substitution.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:07+00:00</t>
+    <t>2026-04-20T13:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4125,7 +4125,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>165</v>
       </c>
@@ -4140,13 +4140,13 @@
         <v>62</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>74</v>
@@ -4228,7 +4228,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>169</v>
       </c>
@@ -4243,13 +4243,13 @@
         <v>170</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>74</v>
@@ -4537,7 +4537,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>183</v>
       </c>
@@ -4552,13 +4552,13 @@
         <v>184</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
